--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -561,6 +631,20 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -623,6 +707,20 @@
           <t>ppjDR086</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -681,6 +779,20 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -743,6 +855,20 @@
           <t>AovF1Mia</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -801,6 +927,20 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -859,6 +999,20 @@
           <t>WdKOwxDM</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -917,6 +1071,20 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -975,6 +1143,20 @@
           <t>2XrRecc3</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1037,6 +1219,20 @@
           <t>ppjDR086</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1099,2010 +1295,3297 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45514.45833333334</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U5cORazJ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dCkAk3SP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lAUlrLKa</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>fNaktakC</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2m3cvwKO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2g67Vsyf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45528.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t xml:space="preserve">wembley stadium
   london </t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E22" t="n">
         <v>90000</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="H22" t="n">
+        <v>48</v>
+      </c>
+      <c r="I22" t="n">
         <v>482</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K22" t="n">
         <v>2024</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>fa community shield</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="P22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>180</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>73</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="V22" t="n">
+        <v>83</v>
+      </c>
+      <c r="W22" t="n">
+        <v>23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>169</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>OMDVg8x9</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">brunton park
   carlisle </t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E23" t="n">
         <v>17949</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>dUzTIwSF</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>hSUajdSS</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="H23" t="n">
+        <v>48</v>
+      </c>
+      <c r="I23" t="n">
         <v>484</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="K23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>jXcAnQUr</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">brisbane road
   london </t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E24" t="n">
         <v>9271</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KKyYcus9</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>ChwgcrNJ</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="H24" t="n">
+        <v>48</v>
+      </c>
+      <c r="I24" t="n">
         <v>484</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="K24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>fRe0c20b</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">edgeley park
   stockport </t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E25" t="n">
         <v>10841</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>IX6WjNvr</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>6Nl8nagD</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="H25" t="n">
+        <v>48</v>
+      </c>
+      <c r="I25" t="n">
         <v>484</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="K25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>z3dmTMMO</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>CnnJp4ae</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">holker street
   barrow in furness </t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E26" t="n">
         <v>6500</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>KKJL7QXd</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>U3lM3y4e</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="H26" t="n">
+        <v>48</v>
+      </c>
+      <c r="I26" t="n">
         <v>484</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="K26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>bw1zAKS6</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">toughsheet community stadium
   bolton </t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E27" t="n">
         <v>28723</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Or1bBrWD</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>t6G9wMZN</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H27" t="n">
+        <v>48</v>
+      </c>
+      <c r="I27" t="n">
         <v>484</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="K27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>GINCsvmn</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B28" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">ashton gate stadium
   bristol </t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E28" t="n">
         <v>27000</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>MahqU27I</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>GOvB22xg</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H28" t="n">
+        <v>48</v>
+      </c>
+      <c r="I28" t="n">
         <v>484</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="K28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>KrrdAMyI</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>x6klsVh3</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">hayes lane
   london </t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E29" t="n">
         <v>5000</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Opdcd08Q</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>4KREuF43</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="H29" t="n">
+        <v>48</v>
+      </c>
+      <c r="I29" t="n">
         <v>484</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>b3pRrrU7</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">pirelli stadium
   burton upon trent </t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E30" t="n">
         <v>6912</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>nwCtJaJT</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>8EFIJthC</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="H30" t="n">
+        <v>48</v>
+      </c>
+      <c r="I30" t="n">
         <v>484</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>WfkfPdXH</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">abbey stadium
   cambridge </t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E31" t="n">
         <v>7937</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>lnb8EJRp</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>lrMHUHDc</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="H31" t="n">
+        <v>48</v>
+      </c>
+      <c r="I31" t="n">
         <v>484</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="K31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>SMr3Nz2U</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">cardiff city stadium
   cardiff </t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E32" t="n">
         <v>33280</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>hO8wh6aP</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>GILi6JC9</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>48</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="H32" t="n">
+        <v>48</v>
+      </c>
+      <c r="I32" t="n">
         <v>484</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="K32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>K6xezbY7</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>xYBLuIHb</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">the valley
   london </t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E33" t="n">
         <v>27111</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>fXf5mQ7t</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>SWk4muv7</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>48</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H33" t="n">
+        <v>48</v>
+      </c>
+      <c r="I33" t="n">
         <v>484</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="K33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
         <is>
           <t>W00wmLO0</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>6os5wmhS</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">colchester community stadium
   colchester </t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E34" t="n">
         <v>10105</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>xYu73rNn</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>EmlVDpVP</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>48</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H34" t="n">
+        <v>48</v>
+      </c>
+      <c r="I34" t="n">
         <v>484</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="K34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>Kl7vhn7L</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B35" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">the broadfield stadium
   crawley </t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E35" t="n">
         <v>6134</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>QVmLl54o</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>xSloasB8</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>48</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H35" t="n">
+        <v>48</v>
+      </c>
+      <c r="I35" t="n">
         <v>484</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="K35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>nw6fJO5K</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n">
+      <c r="B36" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">pride park
   derby </t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E36" t="n">
         <v>33597</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Iug0YO0Q</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>dQIMIN5n</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>48</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="H36" t="n">
+        <v>48</v>
+      </c>
+      <c r="I36" t="n">
         <v>484</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="K36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>bHPacsq1</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n">
+      <c r="B37" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">highbury stadium
   fleetwood </t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E37" t="n">
         <v>5327</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>tCZ3D68d</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>CCBWpzjj</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>48</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="H37" t="n">
+        <v>48</v>
+      </c>
+      <c r="I37" t="n">
         <v>484</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>MwmHgKaN</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B38" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">blundell park
   cleethorpes </t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E38" t="n">
         <v>9052</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>OEaiS3za</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>bsc3EJ27</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>48</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="H38" t="n">
+        <v>48</v>
+      </c>
+      <c r="I38" t="n">
         <v>484</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="K38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>lQl9etVA</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">john smith s stadium
   huddersfield </t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E39" t="n">
         <v>24121</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>xxxpBZl2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>zmKRcPKu</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>48</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="H39" t="n">
+        <v>48</v>
+      </c>
+      <c r="I39" t="n">
         <v>484</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>KWD8eLDD</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t xml:space="preserve">lner stadium
   lincoln </t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E40" t="n">
         <v>10669</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>hrHTRs5B</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>CQv5qrFt</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>48</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="H40" t="n">
+        <v>48</v>
+      </c>
+      <c r="I40" t="n">
         <v>484</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>xUXzYQFk</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
+      <c r="B41" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">sixfields stadium
   northampton </t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E41" t="n">
         <v>7798</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>l4P6dwRR</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>hl2V5JIl</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>48</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="H41" t="n">
+        <v>48</v>
+      </c>
+      <c r="I41" t="n">
         <v>484</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="K41" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>CCV9JR0d</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n">
+      <c r="B42" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t xml:space="preserve">carrow road
   norwich </t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E42" t="n">
         <v>27137</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Qo6off6p</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>ANwyQM2M</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>48</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="H42" t="n">
+        <v>48</v>
+      </c>
+      <c r="I42" t="n">
         <v>484</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="K42" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>thqhB2MB</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>bsinRI25</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t xml:space="preserve">kassam stadium
   oxford </t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E43" t="n">
         <v>12500</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>vgOBT43c</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>tWeI85kh</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>48</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="H43" t="n">
+        <v>48</v>
+      </c>
+      <c r="I43" t="n">
         <v>484</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="K43" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>GbaVU03t</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B44" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t xml:space="preserve">fratton park
   portsmouth </t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E44" t="n">
         <v>21944</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>zckREQFJ</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>6uz2cJBL</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>48</v>
-      </c>
-      <c r="I34" t="n">
+      <c r="H44" t="n">
+        <v>48</v>
+      </c>
+      <c r="I44" t="n">
         <v>484</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="K44" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>Cxq57r8g</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>tOTmlbNp</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n">
+      <c r="B45" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t xml:space="preserve">deepdale
   preston </t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E45" t="n">
         <v>23408</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>x8IDVcbi</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>48</v>
-      </c>
-      <c r="I35" t="n">
+      <c r="H45" t="n">
+        <v>48</v>
+      </c>
+      <c r="I45" t="n">
         <v>484</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="K45" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>nPQL4PjR</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B46" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">aesseal new york stadium
   rotherham </t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E46" t="n">
         <v>12021</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>KMfM7P4b</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>YacqHHdS</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>48</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="H46" t="n">
+        <v>48</v>
+      </c>
+      <c r="I46" t="n">
         <v>484</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+      <c r="K46" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>pWhdu9NF</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B47" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t xml:space="preserve">peninsula stadium
   salford </t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E47" t="n">
         <v>5108</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>W4AadhN3</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>hlzYDy5q</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>48</v>
-      </c>
-      <c r="I37" t="n">
+      <c r="H47" t="n">
+        <v>48</v>
+      </c>
+      <c r="I47" t="n">
         <v>484</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="K47" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>6NnRD2Ts</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
+      <c r="B48" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t xml:space="preserve">the croud meadow
   shrewsbury </t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E48" t="n">
         <v>9877</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>EqfQ6qK4</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>EwJVdqzn</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>48</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="H48" t="n">
+        <v>48</v>
+      </c>
+      <c r="I48" t="n">
         <v>484</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="K48" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>2FcwTvYh</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B49" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t xml:space="preserve">swansea com stadium
   swansea </t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E49" t="n">
         <v>21088</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>K6xezbY7</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>WvZyDeKk</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>48</v>
-      </c>
-      <c r="I39" t="n">
+      <c r="H49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" t="n">
         <v>484</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
+      <c r="K49" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>hO8wh6aP</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>EBSD6oME</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B50" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t xml:space="preserve">prenton park
   birkenhead </t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E50" t="n">
         <v>16587</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>jVhkb1QE</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>6ZvdGuYf</t>
         </is>
       </c>
-      <c r="H40" t="n">
-        <v>48</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H50" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" t="n">
         <v>484</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="K50" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>WSQqW4p2</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B51" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t xml:space="preserve">bescot stadium
   walsall </t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E51" t="n">
         <v>11300</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>YgrfcLuL</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>ve14a3l4</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>48</v>
-      </c>
-      <c r="I41" t="n">
+      <c r="H51" t="n">
+        <v>48</v>
+      </c>
+      <c r="I51" t="n">
         <v>484</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="K51" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>vaX1LmWq</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B52" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
         <is>
           <t xml:space="preserve">vicarage road
   watford </t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E52" t="n">
         <v>22200</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>UmMRoGzp</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>f9KDxtkU</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>48</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="H52" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" t="n">
         <v>484</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="K52" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>SlybbadF</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>n1hhaOVo</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n">
+      <c r="B53" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t xml:space="preserve">dw stadium
   wigan </t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E53" t="n">
         <v>25133</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>MgHlK2Na</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>UNGEKMx6</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>48</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="H53" t="n">
+        <v>48</v>
+      </c>
+      <c r="I53" t="n">
         <v>484</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
+      <c r="K53" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>vyoZBtbf</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n">
+      <c r="B54" s="2" t="n">
         <v>45517.66666666666</v>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
         <is>
           <t xml:space="preserve">bramall lane
   sheffield </t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E54" t="n">
         <v>32050</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>MeKPSerA</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>IgO7K1ZA</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>48</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="H54" t="n">
+        <v>48</v>
+      </c>
+      <c r="I54" t="n">
         <v>484</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="K54" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>634r8bcJ</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n">
+      <c r="B55" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
         <is>
           <t xml:space="preserve">mkm stadium
   hull </t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E55" t="n">
         <v>25586</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>S66R0t75</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>llcCvIcG</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>48</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="H55" t="n">
+        <v>48</v>
+      </c>
+      <c r="I55" t="n">
         <v>484</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
+      <c r="K55" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>pbFTwdnB</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n">
+      <c r="B56" s="2" t="n">
         <v>45518.65625</v>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t xml:space="preserve">home park
   plymouth </t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E56" t="n">
         <v>17000</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>WpGM6ELj</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>jizXHcsM</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>48</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="H56" t="n">
+        <v>48</v>
+      </c>
+      <c r="I56" t="n">
         <v>484</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="K56" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>697ha3El</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B57" s="2" t="n">
         <v>45518.66666666666</v>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t xml:space="preserve">elland road
   leeds </t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E57" t="n">
         <v>37792</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>tUxUbLR2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>6F0lvLNC</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>48</v>
-      </c>
-      <c r="I47" t="n">
+      <c r="H57" t="n">
+        <v>48</v>
+      </c>
+      <c r="I57" t="n">
         <v>484</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="K57" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>xxxpBZl2</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,70 +505,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_miss_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>sum_val_player_miss_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
@@ -638,13 +603,6 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -714,13 +672,6 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -786,13 +737,6 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -862,13 +806,6 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -934,13 +871,6 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,13 +936,6 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1078,13 +1001,6 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1150,13 +1066,6 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1226,13 +1135,6 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1302,36 +1204,34 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.35416666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>45514.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">wembley stadium
+  london </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31876</v>
+        <v>90000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1343,13 +1243,13 @@
         <v>48</v>
       </c>
       <c r="I12" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1358,12 +1258,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>fa community shield</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1371,58 +1271,65 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>155</v>
+      </c>
+      <c r="U12" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25486</v>
+        <v>17949</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>48</v>
       </c>
       <c r="I13" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>20242025</v>
@@ -1434,19 +1341,11 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1454,51 +1353,44 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
+          <t xml:space="preserve">brisbane road
   london </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>26600</v>
+        <v>9271</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>20242025</v>
@@ -1510,15 +1402,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1526,51 +1414,44 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.64583333334</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>55097</v>
+        <v>10841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>20242025</v>
@@ -1582,17 +1463,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>z3dmTMMO</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1602,51 +1479,44 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32384</v>
+        <v>6500</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>48</v>
       </c>
       <c r="I16" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>20242025</v>
@@ -1658,7 +1528,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1670,51 +1540,44 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>62850</v>
+        <v>28723</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>20242025</v>
@@ -1726,19 +1589,11 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1746,51 +1601,44 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45517.65625</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>42789</v>
+        <v>27000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>20242025</v>
@@ -1802,13 +1650,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -1818,51 +1666,44 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11307</v>
+        <v>5000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>20242025</v>
@@ -1874,19 +1715,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1894,51 +1727,44 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.41666666666</v>
+        <v>45517.65625</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>31750</v>
+        <v>6912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>20242025</v>
@@ -1950,15 +1776,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>premier league</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1966,51 +1788,44 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61276</v>
+        <v>7937</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>20242025</v>
@@ -2022,14 +1837,10 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -2038,59 +1849,47 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45514.45833333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90000</v>
+        <v>33280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2099,89 +1898,50 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>fa community shield</t>
+          <t>efl cup</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V22" t="n">
-        <v>83</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>169</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>82</v>
-      </c>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17949</v>
+        <v>27111</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2207,7 +1967,11 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -2215,41 +1979,34 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9271</v>
+        <v>10105</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2283,41 +2040,34 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10841</v>
+        <v>6134</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2343,11 +2093,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -2355,18 +2101,11 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2375,21 +2114,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6500</v>
+        <v>33597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2423,18 +2162,11 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2443,21 +2175,21 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28723</v>
+        <v>5327</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2491,18 +2223,11 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2511,21 +2236,21 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27000</v>
+        <v>9052</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2551,11 +2276,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2563,18 +2284,11 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2583,21 +2297,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5000</v>
+        <v>24121</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2622,7 +2336,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2631,18 +2349,11 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -2651,21 +2362,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6912</v>
+        <v>10669</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2699,18 +2410,11 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -2719,21 +2423,21 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7937</v>
+        <v>7798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2767,18 +2471,11 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -2787,21 +2484,21 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33280</v>
+        <v>27137</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2828,7 +2525,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -2839,18 +2536,11 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -2859,21 +2549,21 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27111</v>
+        <v>12500</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2899,11 +2589,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2911,18 +2597,11 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -2931,21 +2610,21 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10105</v>
+        <v>21944</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2971,7 +2650,11 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2979,18 +2662,11 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -2999,21 +2675,21 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6134</v>
+        <v>23408</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3039,7 +2715,11 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -3047,18 +2727,11 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3067,21 +2740,21 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>33597</v>
+        <v>12021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3115,18 +2788,11 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3135,21 +2801,21 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5327</v>
+        <v>5108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3183,18 +2849,11 @@
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3203,21 +2862,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9052</v>
+        <v>9877</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3251,18 +2910,11 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3271,21 +2923,21 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24121</v>
+        <v>21088</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3312,7 +2964,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -3323,18 +2975,11 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3343,21 +2988,21 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10669</v>
+        <v>16587</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -3391,18 +3036,11 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3411,21 +3049,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7798</v>
+        <v>11300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3459,18 +3097,11 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -3479,21 +3110,21 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27137</v>
+        <v>22200</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3520,7 +3151,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>SlybbadF</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -3531,18 +3162,11 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -3551,21 +3175,21 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12500</v>
+        <v>25133</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3599,41 +3223,34 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21944</v>
+        <v>32050</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3659,11 +3276,7 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -3671,41 +3284,34 @@
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23408</v>
+        <v>25586</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -3730,12 +3336,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -3743,41 +3349,34 @@
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12021</v>
+        <v>17000</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3811,41 +3410,34 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.66666666666</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5108</v>
+        <v>37792</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3870,8 +3462,16 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>xxxpBZl2</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3879,713 +3479,6 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>6NnRD2Ts</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>9877</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>EqfQ6qK4</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>EwJVdqzn</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>48</v>
-      </c>
-      <c r="I48" t="n">
-        <v>484</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>2FcwTvYh</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>WvZyDeKk</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>48</v>
-      </c>
-      <c r="I49" t="n">
-        <v>484</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>EBSD6oME</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>16587</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>jVhkb1QE</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6ZvdGuYf</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" t="n">
-        <v>484</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>WSQqW4p2</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>YgrfcLuL</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>ve14a3l4</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>48</v>
-      </c>
-      <c r="I51" t="n">
-        <v>484</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>vaX1LmWq</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>f9KDxtkU</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>48</v>
-      </c>
-      <c r="I52" t="n">
-        <v>484</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>n1hhaOVo</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>25133</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>MgHlK2Na</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>UNGEKMx6</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>48</v>
-      </c>
-      <c r="I53" t="n">
-        <v>484</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>vyoZBtbf</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>32050</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>IgO7K1ZA</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>48</v>
-      </c>
-      <c r="I54" t="n">
-        <v>484</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>25586</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S66R0t75</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>llcCvIcG</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>48</v>
-      </c>
-      <c r="I55" t="n">
-        <v>484</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>pbFTwdnB</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>17000</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>WpGM6ELj</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>jizXHcsM</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>48</v>
-      </c>
-      <c r="I56" t="n">
-        <v>484</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>37792</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>48</v>
-      </c>
-      <c r="I57" t="n">
-        <v>484</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,76 +503,6 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -631,20 +561,6 @@
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -707,20 +623,6 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -779,20 +681,6 @@
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -855,20 +743,6 @@
           <t>AovF1Mia</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -927,20 +801,6 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -999,20 +859,6 @@
           <t>WdKOwxDM</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1071,20 +917,6 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1143,20 +975,6 @@
           <t>2XrRecc3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1219,20 +1037,6 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1295,20 +1099,6 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1371,20 +1161,6 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1447,20 +1223,6 @@
           <t>6uz2cJBL</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1519,20 +1281,6 @@
           <t>UsushcZr</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1595,20 +1343,6 @@
           <t>Qo6off6p</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1663,20 +1397,6 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1739,20 +1459,6 @@
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1811,20 +1517,6 @@
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1887,20 +1579,6 @@
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1959,20 +1637,6 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2031,66 +1695,47 @@
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45514.45833333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>90000</v>
+        <v>17949</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2024</v>
+        <v>20242025</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2099,66 +1744,16 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>fa community shield</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>180</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V22" t="n">
-        <v>83</v>
-      </c>
-      <c r="W22" t="n">
-        <v>23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>169</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>82</v>
-      </c>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2167,21 +1762,21 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">brisbane road
+  london </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17949</v>
+        <v>9271</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2208,25 +1803,11 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -2235,21 +1816,21 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9271</v>
+        <v>10841</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2275,49 +1856,39 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>z3dmTMMO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10841</v>
+        <v>6500</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2343,30 +1914,12 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2375,21 +1928,21 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6500</v>
+        <v>28723</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2416,25 +1969,11 @@
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2443,21 +1982,21 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28723</v>
+        <v>27000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2483,26 +2022,16 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2511,21 +2040,21 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27000</v>
+        <v>5000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2551,30 +2080,12 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2583,21 +2094,21 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5000</v>
+        <v>6912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2624,25 +2135,11 @@
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -2651,21 +2148,21 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6912</v>
+        <v>7937</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2692,25 +2189,11 @@
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -2719,21 +2202,21 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7937</v>
+        <v>33280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -2758,27 +2241,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>K6xezbY7</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -2787,21 +2260,21 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33280</v>
+        <v>27111</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2826,31 +2299,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -2859,21 +2318,21 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27111</v>
+        <v>10105</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2899,30 +2358,12 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -2931,21 +2372,21 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10105</v>
+        <v>6134</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2972,25 +2413,11 @@
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -2999,21 +2426,21 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6134</v>
+        <v>33597</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3040,25 +2467,11 @@
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -3067,21 +2480,21 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>33597</v>
+        <v>5327</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3108,25 +2521,11 @@
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -3135,21 +2534,21 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5327</v>
+        <v>9052</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3176,25 +2575,11 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -3203,21 +2588,21 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9052</v>
+        <v>24121</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3242,27 +2627,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -3271,21 +2646,21 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>24121</v>
+        <v>10669</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3310,31 +2685,13 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -3343,21 +2700,21 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10669</v>
+        <v>7798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -3384,25 +2741,11 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -3411,21 +2754,21 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7798</v>
+        <v>27137</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3450,27 +2793,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -3479,21 +2812,21 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>27137</v>
+        <v>12500</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3518,31 +2851,13 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -3551,21 +2866,21 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12500</v>
+        <v>21944</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3591,26 +2906,16 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -3619,21 +2924,21 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21944</v>
+        <v>23408</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3661,28 +2966,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -3691,21 +2982,21 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23408</v>
+        <v>12021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -3731,30 +3022,12 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -3763,21 +3036,21 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12021</v>
+        <v>5108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3804,25 +3077,11 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -3831,21 +3090,21 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5108</v>
+        <v>9877</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3872,25 +3131,11 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -3899,21 +3144,21 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9877</v>
+        <v>21088</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3938,27 +3183,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -3967,21 +3202,21 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>21088</v>
+        <v>16587</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -4006,31 +3241,13 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -4039,21 +3256,21 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16587</v>
+        <v>11300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -4080,25 +3297,11 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
@@ -4107,21 +3310,21 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11300</v>
+        <v>22200</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -4146,27 +3349,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SlybbadF</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -4175,21 +3368,21 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22200</v>
+        <v>25133</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -4214,54 +3407,36 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>25133</v>
+        <v>32050</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4288,48 +3463,34 @@
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45517.66666666666</v>
+        <v>45518.65625</v>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>32050</v>
+        <v>25586</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>IgO7K1ZA</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -4354,27 +3515,17 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>tUxUbLR2</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
@@ -4383,21 +3534,21 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25586</v>
+        <v>17000</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -4422,54 +3573,36 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45518.66666666666</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17000</v>
+        <v>37792</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -4494,98 +3627,16 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45518.66666666666</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>37792</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>48</v>
-      </c>
-      <c r="I57" t="n">
-        <v>484</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>xxxpBZl2</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45528.35416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">amex stadium
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45528.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">selhurst park
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45528.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">craven cottage
@@ -695,7 +710,12 @@
       <c r="B5" s="2" t="n">
         <v>45528.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">etihad stadium
@@ -757,7 +777,12 @@
       <c r="B6" s="2" t="n">
         <v>45528.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">st  mary s stadium
@@ -811,7 +836,12 @@
       <c r="B7" s="2" t="n">
         <v>45528.45833333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">tottenham hotspur stadium
@@ -873,7 +903,12 @@
       <c r="B8" s="2" t="n">
         <v>45528.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">villa park
@@ -931,7 +966,12 @@
       <c r="B9" s="2" t="n">
         <v>45529.41666666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">vitality stadium
@@ -993,7 +1033,12 @@
       <c r="B10" s="2" t="n">
         <v>45529.41666666666</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
@@ -1051,7 +1096,12 @@
       <c r="B11" s="2" t="n">
         <v>45529.52083333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">anfield
@@ -1693,1436 +1743,6 @@
       <c r="O21" t="inlineStr">
         <is>
           <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>rRQ6H30k</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45531.63541666666</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">riverside stadium
-  middlesbrough </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>34742</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>6F0lvLNC</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>hSUajdSS</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>48</v>
-      </c>
-      <c r="I22" t="n">
-        <v>484</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>dUjtW2Fr</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oakwell
-  barnsley </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>23287</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>UNGEKMx6</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MeKPSerA</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>48</v>
-      </c>
-      <c r="I23" t="n">
-        <v>484</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>MFnpCm7C</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KKJL7QXd</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Iug0YO0Q</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>48</v>
-      </c>
-      <c r="I24" t="n">
-        <v>484</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>UsklUtpe</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ewood park
-  blackburn </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>31367</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>8EFIJthC</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>48</v>
-      </c>
-      <c r="I25" t="n">
-        <v>484</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddFjPf2b</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>31876</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>QVmLl54o</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>48</v>
-      </c>
-      <c r="I26" t="n">
-        <v>484</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Sh9BS8ig</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coventry building society arena
-  coventry </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>32753</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>GOvB22xg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>vgOBT43c</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>48</v>
-      </c>
-      <c r="I27" t="n">
-        <v>484</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dAfPwfHi</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>hlzYDy5q</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>48</v>
-      </c>
-      <c r="I28" t="n">
-        <v>484</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>pWQ6LC1N</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>5327</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>tCZ3D68d</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KMfM7P4b</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>48</v>
-      </c>
-      <c r="I29" t="n">
-        <v>484</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>jiUEFsV1</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>9052</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>OEaiS3za</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>llcCvIcG</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>48</v>
-      </c>
-      <c r="I30" t="n">
-        <v>484</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>dY0SOQjI</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">envirovent stadium
-  harrogate </t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CQv5qrFt</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>x8IDVcbi</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>48</v>
-      </c>
-      <c r="I31" t="n">
-        <v>484</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>hO8aNYWA</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>32261</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>jVhkb1QE</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>48</v>
-      </c>
-      <c r="I32" t="n">
-        <v>484</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>vDA9yPiL</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the den
-  london </t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>20146</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>KKyYcus9</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>48</v>
-      </c>
-      <c r="I33" t="n">
-        <v>484</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>hzeTFV7m</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">loftus road
-  london </t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>18439</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>lrMHUHDc</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>48</v>
-      </c>
-      <c r="I34" t="n">
-        <v>484</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Q9rcSKE7</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>9877</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>EqfQ6qK4</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Or1bBrWD</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>48</v>
-      </c>
-      <c r="I35" t="n">
-        <v>484</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>zJCJQnM5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>11300</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>YgrfcLuL</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>xxxpBZl2</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>48</v>
-      </c>
-      <c r="I36" t="n">
-        <v>484</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>tUxUbLR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>QkntzCGG</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22200</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>UmMRoGzp</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>WpGM6ELj</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>48</v>
-      </c>
-      <c r="I37" t="n">
-        <v>484</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>SlybbadF</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Wn71woN8</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45531.66666666666</v>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  andrew s stadium
-  birmingham </t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>29409</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>SWk4muv7</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>48</v>
-      </c>
-      <c r="I38" t="n">
-        <v>484</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkqxE9x0</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45531.66666666666</v>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>25486</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>48</v>
-      </c>
-      <c r="I39" t="n">
-        <v>484</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>GEugARyP</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45532.64583333334</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>z3dmTMMO</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>48</v>
-      </c>
-      <c r="I40" t="n">
-        <v>484</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>6Nl8nagD</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>U32wGjPp</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the cherry red records stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>9215</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>4KREuF43</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>48</v>
-      </c>
-      <c r="I41" t="n">
-        <v>484</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>hGzqjO6E</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>33280</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>48</v>
-      </c>
-      <c r="I42" t="n">
-        <v>484</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>OrHrRGXo</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>10105</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>xYu73rNn</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>48</v>
-      </c>
-      <c r="I43" t="n">
-        <v>484</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>WQF2UUMt</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>21088</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>K6xezbY7</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>hl2V5JIl</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>48</v>
-      </c>
-      <c r="I44" t="n">
-        <v>484</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>hO8wh6aP</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>rkazN4LU</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45532.65625</v>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">london stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>48</v>
-      </c>
-      <c r="I45" t="n">
-        <v>484</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>hxlYyYo4</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>45532.66666666666</v>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>48</v>
-      </c>
-      <c r="I46" t="n">
-        <v>484</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
         </is>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -570,6 +640,48 @@
           <t>lId4TMwf</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>194</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>182</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>316</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -637,6 +749,20 @@
           <t>6uz2cJBL</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -700,6 +826,34 @@
           <t>UsushcZr</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X4" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>138</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -767,6 +921,48 @@
           <t>Qo6off6p</t>
         </is>
       </c>
+      <c r="P5" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>174</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>68</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>82</v>
+      </c>
+      <c r="W5" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>181.1666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>426</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>441</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -826,6 +1022,34 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>189</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>82</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -893,6 +1117,48 @@
           <t>lId4TMwf</t>
         </is>
       </c>
+      <c r="P7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>82</v>
+      </c>
+      <c r="U7" t="n">
+        <v>39500000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>443</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>40625000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>479</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -956,794 +1222,47 @@
           <t>UDg08Ohm</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>11307</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>48</v>
-      </c>
-      <c r="I9" t="n">
-        <v>481</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">england d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>48</v>
-      </c>
-      <c r="I10" t="n">
-        <v>481</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>61276</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>48</v>
-      </c>
-      <c r="I11" t="n">
-        <v>481</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>ERWFdKZh</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45535.35416666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>60704</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>8QPOfb45</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45535.45833333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>17250</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>x6HuiG3U</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45535.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>SUdkBJln</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45535.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>lpob9cJb</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45535.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>32261</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2Fanm72d</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45535.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INsZAAf3</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45535.5625</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">london stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
-        <v>481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
+      <c r="P8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>190</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>161</v>
+      </c>
+      <c r="U8" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>164</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>158</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31876</v>
+        <v>11307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +632,89 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>194</v>
+        <v>180.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="U2" t="n">
-        <v>10500000</v>
+        <v>50000000</v>
       </c>
       <c r="V2" t="n">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="W2" t="n">
-        <v>24.5</v>
+        <v>24.85714285714286</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>186.4285714285714</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA2" t="n">
-        <v>316</v>
+        <v>540</v>
       </c>
       <c r="AB2" t="n">
-        <v>92000000</v>
+        <v>188375000</v>
       </c>
       <c r="AC2" t="n">
-        <v>333</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>25486</v>
+        <v>31750</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -739,23 +739,33 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>200</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>77</v>
+      </c>
+      <c r="U3" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>79</v>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -767,35 +777,35 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26600</v>
+        <v>61276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -820,12 +830,12 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -837,7 +847,7 @@
         <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>188.5</v>
+        <v>177.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
@@ -846,47 +856,42 @@
         <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="AB4" t="n">
-        <v>7000000</v>
+        <v>23000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">salisbury m 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.35416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55097</v>
+        <v>60704</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -913,89 +918,56 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>174</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>68</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>82</v>
-      </c>
-      <c r="W5" t="n">
-        <v>25.83333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>181.1666666666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>426</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>21800000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>441</v>
-      </c>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32384</v>
+        <v>17250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1022,27 +994,13 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>189</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>72</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>82</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1054,35 +1012,30 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62850</v>
+        <v>39572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1109,89 +1062,56 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>187</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>39500000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>85</v>
-      </c>
-      <c r="W7" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="X7" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>443</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>40625000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>479</v>
-      </c>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">oliver m 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>42789</v>
+        <v>29673</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1216,54 +1136,470 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tvOWhxZH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>190</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>161</v>
-      </c>
-      <c r="U8" t="n">
-        <v>52000000</v>
-      </c>
-      <c r="V8" t="n">
-        <v>164</v>
-      </c>
-      <c r="W8" t="n">
-        <v>25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>183</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>158</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>44000000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>165</v>
-      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>z1q67ylB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.35416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11307</v>
+        <v>60704</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,89 +557,42 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>232</v>
-      </c>
-      <c r="U2" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>237</v>
-      </c>
-      <c r="W2" t="n">
-        <v>24.85714285714286</v>
-      </c>
-      <c r="X2" t="n">
-        <v>186.4285714285714</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>540</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>188375000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>576</v>
+          <t>AovF1Mia</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">england d 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31750</v>
+        <v>17250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -740,72 +618,35 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
+          <t xml:space="preserve">goodison park
   liverpool </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>61276</v>
+        <v>39572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -832,66 +673,42 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>23</v>
-      </c>
-      <c r="X4" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>153</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>160</v>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.35416666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60704</v>
+        <v>29673</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -918,33 +735,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -953,21 +752,21 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>17250</v>
+        <v>32261</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -992,27 +791,17 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1021,21 +810,21 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39572</v>
+        <v>30404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1060,58 +849,36 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29673</v>
+        <v>62500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1138,52 +905,42 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32261</v>
+        <v>40341</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1210,52 +967,42 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30404</v>
+        <v>52305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1280,50 +1027,44 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>62500</v>
+        <v>75635</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1350,7 +1091,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1358,248 +1099,6 @@
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tvOWhxZH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U11vkTXq</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>z1q67ylB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45535.35416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">emirates stadium
@@ -565,6 +640,34 @@
           <t>AovF1Mia</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>241</v>
+      </c>
+      <c r="U2" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>249</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -575,7 +678,12 @@
       <c r="B3" s="2" t="n">
         <v>45535.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">brentford community stadium
@@ -619,6 +727,48 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>233</v>
+      </c>
+      <c r="U3" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>240</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>144</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -629,7 +779,12 @@
       <c r="B4" s="2" t="n">
         <v>45535.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">goodison park
@@ -680,6 +835,48 @@
         <is>
           <t>WdKOwxDM</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>190</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>220</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>250</v>
+      </c>
+      <c r="W4" t="n">
+        <v>25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>232</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -691,7 +888,12 @@
       <c r="B5" s="2" t="n">
         <v>45535.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">portman road
@@ -739,6 +941,34 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>349</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>363</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -749,7 +979,12 @@
       <c r="B6" s="2" t="n">
         <v>45535.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">king power stadium
@@ -797,6 +1032,48 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>138</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>148</v>
+      </c>
+      <c r="W6" t="n">
+        <v>26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>244</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -807,7 +1084,12 @@
       <c r="B7" s="2" t="n">
         <v>45535.45833333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">city ground
@@ -851,6 +1133,34 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -861,7 +1171,12 @@
       <c r="B8" s="2" t="n">
         <v>45535.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">london stadium
@@ -912,6 +1227,48 @@
         <is>
           <t>ppjDR086</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>175</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>76</v>
+      </c>
+      <c r="W8" t="n">
+        <v>19</v>
+      </c>
+      <c r="X8" t="n">
+        <v>174</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -923,7 +1280,12 @@
       <c r="B9" s="2" t="n">
         <v>45536.39583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">stamford bridge
@@ -975,6 +1337,20 @@
           <t>2XrRecc3</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -985,7 +1361,12 @@
       <c r="B10" s="2" t="n">
         <v>45536.39583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">st  james  park
@@ -1036,6 +1417,48 @@
         <is>
           <t>hA1Zm19f</t>
         </is>
+      </c>
+      <c r="P10" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>188</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>471</v>
+      </c>
+      <c r="U10" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>490</v>
+      </c>
+      <c r="W10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>187</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>159</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -1047,7 +1470,12 @@
       <c r="B11" s="2" t="n">
         <v>45536.5</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">old trafford
@@ -1099,6 +1527,622 @@
           <t>ppjDR086</t>
         </is>
       </c>
+      <c r="P11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>396</v>
+      </c>
+      <c r="U11" t="n">
+        <v>120500000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>416</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>40341</v>
+        <v>32384</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -630,63 +555,40 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.39583333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52305</v>
+        <v>31876</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -713,89 +615,42 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>188</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.833333333333333</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>471</v>
-      </c>
-      <c r="U3" t="n">
-        <v>106000000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>490</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>158</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>162</v>
+          <t>Qo6off6p</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>75635</v>
+        <v>25486</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -822,42 +677,428 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>181.8</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>396</v>
-      </c>
-      <c r="U4" t="n">
-        <v>120500000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>416</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>31750</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,602 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,290 +503,1213 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45556.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">barrott s 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>481</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E8" t="n">
         <v>62850</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>48</v>
-      </c>
-      <c r="I2" t="n">
-        <v>481</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>hA1Zm19f</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>184</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>81</v>
-      </c>
-      <c r="U2" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>83</v>
-      </c>
-      <c r="W2" t="n">
-        <v>25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>183</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>416</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>289500000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Of1jzRNE</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WSzc94ws</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
   wolverhampton </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E18" t="n">
         <v>31750</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>48</v>
-      </c>
-      <c r="I3" t="n">
-        <v>481</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>82600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>330</v>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -570,6 +640,34 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>203</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>23375000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>229</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -580,7 +678,12 @@
       <c r="B3" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">villa park
@@ -624,6 +727,48 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>188.3333333333333</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>240</v>
+      </c>
+      <c r="U3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>244</v>
+      </c>
+      <c r="W3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>138</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14475000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,7 +779,12 @@
       <c r="B4" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">craven cottage
@@ -681,6 +831,34 @@
         <is>
           <t>WSzc94ws</t>
         </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>311</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>82600000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="5">
@@ -692,7 +870,12 @@
       <c r="B5" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">king power stadium
@@ -743,6 +926,48 @@
         <is>
           <t>lId4TMwf</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>138</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>148</v>
+      </c>
+      <c r="W5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>185</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>293</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>22300000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>322</v>
       </c>
     </row>
     <row r="6">
@@ -754,7 +979,12 @@
       <c r="B6" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">anfield
@@ -805,6 +1035,48 @@
         <is>
           <t>WdKOwxDM</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>168</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>85</v>
+      </c>
+      <c r="W6" t="n">
+        <v>24</v>
+      </c>
+      <c r="X6" t="n">
+        <v>175</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -816,7 +1088,12 @@
       <c r="B7" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">st  mary s stadium
@@ -863,6 +1140,48 @@
         <is>
           <t>Qo6off6p</t>
         </is>
+      </c>
+      <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>189</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>72</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>82</v>
+      </c>
+      <c r="W7" t="n">
+        <v>29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>183</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -874,7 +1193,12 @@
       <c r="B8" s="2" t="n">
         <v>45556.45833333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">tottenham hotspur stadium
@@ -922,6 +1246,48 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>149</v>
+      </c>
+      <c r="U8" t="n">
+        <v>35300000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>164</v>
+      </c>
+      <c r="W8" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>307</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -932,7 +1298,12 @@
       <c r="B9" s="2" t="n">
         <v>45556.5625</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">selhurst park
@@ -983,6 +1354,48 @@
         <is>
           <t>lId4TMwf</t>
         </is>
+      </c>
+      <c r="P9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>144</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8700000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>157</v>
+      </c>
+      <c r="W9" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="X9" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>314</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>75500000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1047,6 +1460,48 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>145</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>163</v>
+      </c>
+      <c r="W10" t="n">
+        <v>31</v>
+      </c>
+      <c r="X10" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>81</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1114,602 +1569,48 @@
           <t>UDg08Ohm</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>8MkyzwoT</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45563.35416666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>GhdgPLWA</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>60704</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>l6f1Na1N</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>17250</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
-        <v>481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45565.66666666666</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>11307</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>174</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>68</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>82</v>
+      </c>
+      <c r="W11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>181</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>410</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>228500000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>422</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,109 +503,34 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>8MkyzwoT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62850</v>
+        <v>52305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -632,160 +557,1143 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>184</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>81</v>
-      </c>
-      <c r="U2" t="n">
-        <v>32500000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>83</v>
-      </c>
-      <c r="W2" t="n">
-        <v>25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>183</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>416</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>289500000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>428</v>
+          <t>ppjDR086</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>GhdgPLWA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
   wolverhampton </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E8" t="n">
         <v>31750</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6uz2cJBL</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>p6ahwuwJ</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>48</v>
-      </c>
-      <c r="I3" t="n">
-        <v>481</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>WSzc94ws</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W3" t="n">
-        <v>25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>311</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>82600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>330</v>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,66 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +573,12 @@
       <c r="B2" s="2" t="n">
         <v>45563.35416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">st  james  park
@@ -564,6 +629,42 @@
         <is>
           <t>ppjDR086</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="S2" t="n">
+        <v>81000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>311</v>
+      </c>
+      <c r="V2" t="n">
+        <v>19</v>
+      </c>
+      <c r="W2" t="n">
+        <v>174</v>
+      </c>
+      <c r="X2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +676,12 @@
       <c r="B3" s="2" t="n">
         <v>45563.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">emirates stadium
@@ -626,6 +732,42 @@
         <is>
           <t>UsushcZr</t>
         </is>
+      </c>
+      <c r="P3" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="R3" t="n">
+        <v>82</v>
+      </c>
+      <c r="S3" t="n">
+        <v>107000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>492</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>192</v>
+      </c>
+      <c r="X3" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>25666.66666666667</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>213</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +779,12 @@
       <c r="B4" s="2" t="n">
         <v>45563.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">brentford community stadium
@@ -684,6 +831,42 @@
         <is>
           <t>6uz2cJBL</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>46500</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>307</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>187</v>
+      </c>
+      <c r="X4" t="n">
+        <v>81</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>71000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -695,7 +878,12 @@
       <c r="B5" s="2" t="n">
         <v>45563.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">stamford bridge
@@ -746,6 +934,42 @@
         <is>
           <t>AovF1Mia</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>126</v>
+      </c>
+      <c r="V5" t="n">
+        <v>37</v>
+      </c>
+      <c r="W5" t="n">
+        <v>175</v>
+      </c>
+      <c r="X5" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -757,7 +981,12 @@
       <c r="B6" s="2" t="n">
         <v>45563.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">goodison park
@@ -808,6 +1037,42 @@
         <is>
           <t>2XrRecc3</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>37500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>145</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185</v>
+      </c>
+      <c r="X6" t="n">
+        <v>74.33333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>33666.66666666666</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>223</v>
       </c>
     </row>
     <row r="7">
@@ -819,7 +1084,12 @@
       <c r="B7" s="2" t="n">
         <v>45563.45833333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">city ground
@@ -863,6 +1133,30 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181</v>
+      </c>
+      <c r="R7" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>78000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>159</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -873,7 +1167,12 @@
       <c r="B8" s="2" t="n">
         <v>45563.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
@@ -920,6 +1219,40 @@
         <is>
           <t>ppjDR086</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>190.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>278</v>
+      </c>
+      <c r="V8" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" t="n">
+        <v>168</v>
+      </c>
+      <c r="X8" t="n">
+        <v>77</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>65000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -931,7 +1264,12 @@
       <c r="B9" s="2" t="n">
         <v>45564.41666666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">portman road
@@ -979,6 +1317,42 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>183</v>
+      </c>
+      <c r="R9" t="n">
+        <v>68</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>67250</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -989,7 +1363,12 @@
       <c r="B10" s="2" t="n">
         <v>45564.52083333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">old trafford
@@ -1041,659 +1420,41 @@
           <t>hA1Zm19f</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KQ2pRs2b</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45565.66666666666</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>11307</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>48</v>
-      </c>
-      <c r="I11" t="n">
-        <v>481</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.35416666666</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>25486</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>SQM1jbV9</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>60704</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bFdtqGNq</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>17250</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>32261</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>55097</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">london stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>l0Zi1FqS</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ltBAlx0M</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>42789</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>nywy5cp3</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
-        <v>481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>fsjksfhd</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>31876</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
+      <c r="P10" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>74750</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>314</v>
+      </c>
+      <c r="V10" t="n">
+        <v>22</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183</v>
+      </c>
+      <c r="X10" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>53000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,35 +567,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>KnvLwLo4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45563.35416666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">attwell s 
+  eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52305</v>
+        <v>29673</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -622,83 +622,79 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
+          <t>Qo6off6p</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
-        <v>187.5</v>
+        <v>183</v>
       </c>
       <c r="R2" t="n">
-        <v>77.75</v>
+        <v>68</v>
       </c>
       <c r="S2" t="n">
-        <v>81000</v>
+        <v>8000</v>
       </c>
       <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>68</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="X2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>67250</v>
+      </c>
+      <c r="Z2" t="n">
         <v>4</v>
       </c>
-      <c r="U2" t="n">
-        <v>311</v>
-      </c>
-      <c r="V2" t="n">
-        <v>19</v>
-      </c>
-      <c r="W2" t="n">
-        <v>174</v>
-      </c>
-      <c r="X2" t="n">
-        <v>68</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA2" t="n">
-        <v>68</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.45833333334</v>
+        <v>45564.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
-  london </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60704</v>
+        <v>75635</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -725,83 +721,83 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>25.83333333333333</v>
+        <v>23.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>179.3333333333333</v>
+        <v>181.75</v>
       </c>
       <c r="R3" t="n">
-        <v>82</v>
+        <v>78.5</v>
       </c>
       <c r="S3" t="n">
-        <v>107000</v>
+        <v>74750</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>492</v>
+        <v>314</v>
       </c>
       <c r="V3" t="n">
-        <v>25.33333333333333</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="X3" t="n">
-        <v>71</v>
+        <v>74.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>25666.66666666667</v>
+        <v>53000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>213</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.45833333334</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17250</v>
+        <v>11307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -826,635 +822,47 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>6uz2cJBL</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>24.75</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>177.75</v>
+        <v>175</v>
       </c>
       <c r="R4" t="n">
-        <v>76.75</v>
+        <v>77</v>
       </c>
       <c r="S4" t="n">
-        <v>46500</v>
+        <v>37000</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>307</v>
+        <v>77</v>
       </c>
       <c r="V4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="X4" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="n">
-        <v>71000</v>
+        <v>14000</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WQcQHwPp</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>48</v>
-      </c>
-      <c r="I5" t="n">
-        <v>481</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>63</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>126</v>
-      </c>
-      <c r="V5" t="n">
-        <v>37</v>
-      </c>
-      <c r="W5" t="n">
-        <v>175</v>
-      </c>
-      <c r="X5" t="n">
-        <v>77</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>52000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>bXkCusHi</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>39572</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>48</v>
-      </c>
-      <c r="I6" t="n">
-        <v>481</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>37500</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>145</v>
-      </c>
-      <c r="V6" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="W6" t="n">
-        <v>185</v>
-      </c>
-      <c r="X6" t="n">
-        <v>74.33333333333333</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>33666.66666666666</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4hy7UG8j</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45563.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>48</v>
-      </c>
-      <c r="I7" t="n">
-        <v>481</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>181</v>
-      </c>
-      <c r="R7" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>78000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>159</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>K0JghK0c</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45563.5625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>48</v>
-      </c>
-      <c r="I8" t="n">
-        <v>481</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>190.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>278</v>
-      </c>
-      <c r="V8" t="n">
-        <v>20</v>
-      </c>
-      <c r="W8" t="n">
-        <v>168</v>
-      </c>
-      <c r="X8" t="n">
-        <v>77</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>65000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>KnvLwLo4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>48</v>
-      </c>
-      <c r="I9" t="n">
-        <v>481</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>183</v>
-      </c>
-      <c r="R9" t="n">
-        <v>68</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>68</v>
-      </c>
-      <c r="V9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>184.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>67250</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SCsTyaGG</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.52083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>48</v>
-      </c>
-      <c r="I10" t="n">
-        <v>481</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>74750</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>314</v>
-      </c>
-      <c r="V10" t="n">
-        <v>22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183</v>
-      </c>
-      <c r="X10" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>53000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>149</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,57 +545,67 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>r3Wq3yFF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29673</v>
+        <v>25486</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,81 +630,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Qo6off6p</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O2" t="n">
+        <v>185.6666666666667</v>
+      </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="R2" t="n">
-        <v>68</v>
+        <v>178000</v>
       </c>
       <c r="S2" t="n">
-        <v>8000</v>
+        <v>36600000</v>
       </c>
       <c r="T2" t="n">
+        <v>237</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>21</v>
+      </c>
+      <c r="W2" t="n">
+        <v>168</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>68</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>184.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>77.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>67250</v>
+        <v>78</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>61000</v>
       </c>
       <c r="AA2" t="n">
-        <v>310</v>
+        <v>31500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>SQM1jbV9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75635</v>
+        <v>60704</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -719,85 +735,87 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
+      <c r="N3" t="n">
+        <v>26</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180.25</v>
       </c>
       <c r="P3" t="n">
-        <v>23.75</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>181.75</v>
+        <v>325</v>
       </c>
       <c r="R3" t="n">
-        <v>78.5</v>
+        <v>540000</v>
       </c>
       <c r="S3" t="n">
-        <v>74750</v>
+        <v>173500000</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
       <c r="U3" t="n">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>22</v>
       </c>
       <c r="W3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="X3" t="n">
-        <v>74.5</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>53000</v>
+        <v>73</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="AA3" t="n">
-        <v>149</v>
+        <v>6000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>bFdtqGNq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11307</v>
+        <v>17250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -822,48 +840,1165 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>309</v>
+      </c>
+      <c r="R4" t="n">
+        <v>258000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>316</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>190.3333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>218</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>134000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>237</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>286</v>
+      </c>
+      <c r="R5" t="n">
+        <v>146000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>298</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>175</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>246</v>
+      </c>
+      <c r="R6" t="n">
+        <v>529000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>260</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>190</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>218</v>
+      </c>
+      <c r="R8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>236</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>314</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>380000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>118100000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>186</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>399</v>
+      </c>
+      <c r="R9" t="n">
+        <v>493000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>411</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>169</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>63000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nywy5cp3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>180</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>128</v>
+      </c>
+      <c r="R10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>146</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>191</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>56000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fsjksfhd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>151</v>
+      </c>
+      <c r="R11" t="n">
+        <v>111000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11800000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>156</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>183</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>241</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>363000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>253</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.35416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>WdKOwxDM</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>175</v>
-      </c>
-      <c r="R4" t="n">
-        <v>77</v>
-      </c>
-      <c r="S4" t="n">
-        <v>37000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>77</v>
-      </c>
-      <c r="V4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W4" t="n">
-        <v>189</v>
-      </c>
-      <c r="X4" t="n">
-        <v>72</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>14000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>72</v>
-      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,35 +577,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45570.35416666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25486</v>
+        <v>42789</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -631,86 +631,86 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
-        <v>185.6666666666667</v>
+        <v>178</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="R2" t="n">
-        <v>178000</v>
+        <v>130000</v>
       </c>
       <c r="S2" t="n">
-        <v>36600000</v>
+        <v>29500000</v>
       </c>
       <c r="T2" t="n">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="U2" t="n">
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>26.5</v>
       </c>
       <c r="W2" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Z2" t="n">
-        <v>61000</v>
+        <v>253000</v>
       </c>
       <c r="AA2" t="n">
-        <v>31500000</v>
+        <v>88000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>60704</v>
+        <v>40341</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -736,86 +736,86 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>180</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>128</v>
+      </c>
+      <c r="R3" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>146</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
         <v>26</v>
       </c>
-      <c r="O3" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325</v>
-      </c>
-      <c r="R3" t="n">
-        <v>540000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>173500000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>329</v>
-      </c>
-      <c r="U3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
       <c r="W3" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="n">
-        <v>20000</v>
+        <v>56000</v>
       </c>
       <c r="AA3" t="n">
-        <v>6000000</v>
+        <v>11500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.45833333334</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17250</v>
+        <v>31876</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -841,86 +841,81 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="O4" t="n">
-        <v>177.75</v>
+        <v>185.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>309</v>
+        <v>162</v>
       </c>
       <c r="R4" t="n">
-        <v>258000</v>
+        <v>253000</v>
       </c>
       <c r="S4" t="n">
-        <v>52000000</v>
+        <v>69500000</v>
       </c>
       <c r="T4" t="n">
-        <v>316</v>
+        <v>167</v>
       </c>
       <c r="U4" t="n">
         <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>23.66666666666667</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>190.3333333333333</v>
+        <v>183</v>
       </c>
       <c r="X4" t="n">
         <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="Z4" t="n">
-        <v>134000</v>
+        <v>363000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19800000</v>
+        <v>104000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AC4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bond d 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.35416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32261</v>
+        <v>62850</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -945,87 +940,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>26.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>286</v>
-      </c>
-      <c r="R5" t="n">
-        <v>146000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14200000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>298</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25</v>
-      </c>
-      <c r="W5" t="n">
-        <v>175</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>53000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bankes p 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>55097</v>
+        <v>26600</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1050,87 +1008,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="O6" t="n">
-        <v>178.3333333333333</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>246</v>
-      </c>
-      <c r="R6" t="n">
-        <v>529000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>260</v>
-      </c>
-      <c r="U6" t="n">
-        <v>9</v>
-      </c>
-      <c r="V6" t="n">
-        <v>29</v>
-      </c>
-      <c r="W6" t="n">
-        <v>190</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>66000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.45833333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62500</v>
+        <v>29673</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1175,35 +1096,30 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>39572</v>
+        <v>75635</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1228,87 +1144,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186.6666666666667</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>218</v>
-      </c>
-      <c r="R8" t="n">
-        <v>130000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>11400000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>236</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>24</v>
-      </c>
-      <c r="W8" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>314</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>380000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>118100000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>333</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42789</v>
+        <v>52305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1333,87 +1212,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>186</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>399</v>
-      </c>
-      <c r="R9" t="n">
-        <v>493000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>411</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" t="n">
-        <v>24</v>
-      </c>
-      <c r="W9" t="n">
-        <v>169</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>63000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.41666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>40341</v>
+        <v>32384</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1438,87 +1280,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>180</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>128</v>
-      </c>
-      <c r="R10" t="n">
-        <v>41000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1750000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>146</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26</v>
-      </c>
-      <c r="W10" t="n">
-        <v>191</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>77</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>56000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>79</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
+        <v>45584.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31876</v>
+        <v>11307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1543,82 +1348,50 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>31</v>
-      </c>
-      <c r="O11" t="n">
-        <v>182</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>151</v>
-      </c>
-      <c r="R11" t="n">
-        <v>111000</v>
-      </c>
-      <c r="S11" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="T11" t="n">
-        <v>156</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="W11" t="n">
-        <v>183</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>241</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>363000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>104000000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>253</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>62850</v>
+        <v>31750</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1663,30 +1436,30 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26600</v>
+        <v>61276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1728,278 +1501,6 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UiYgHRZP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>n9EQB5cm</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45584.45833333334</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>32384</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45584.35416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">tottenham hotspur stadium
@@ -545,6 +630,38 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="O2" t="n">
+        <v>183</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>241</v>
+      </c>
+      <c r="R2" t="n">
+        <v>363000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>104000000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>253</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -555,7 +672,12 @@
       <c r="B3" s="2" t="n">
         <v>45584.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">craven cottage
@@ -596,6 +718,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N3" t="n">
+        <v>29</v>
+      </c>
+      <c r="O3" t="n">
+        <v>190</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>74</v>
+      </c>
+      <c r="R3" t="n">
+        <v>66000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W3" t="n">
+        <v>178</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>130000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>29500000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>82</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +777,12 @@
       <c r="B4" s="2" t="n">
         <v>45584.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">portman road
@@ -648,6 +823,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>184</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>141</v>
+      </c>
+      <c r="R4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>143</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>144</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>98000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>10100000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>162</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +882,12 @@
       <c r="B5" s="2" t="n">
         <v>45584.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">old trafford
@@ -700,6 +928,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>181</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>156</v>
+      </c>
+      <c r="R5" t="n">
+        <v>163000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>160</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25</v>
+      </c>
+      <c r="W5" t="n">
+        <v>177</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>232</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>191000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>239</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +987,12 @@
       <c r="B6" s="2" t="n">
         <v>45584.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">st  james  park
@@ -752,6 +1033,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>187</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>397</v>
+      </c>
+      <c r="R6" t="n">
+        <v>515000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>137100000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>416</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>162</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>253000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>69500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>167</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -763,7 +1092,12 @@
       <c r="B7" s="2" t="n">
         <v>45584.45833333334</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">st  mary s stadium
@@ -804,6 +1138,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>23</v>
+      </c>
+      <c r="O7" t="n">
+        <v>186</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>56000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>161</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>97000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -815,7 +1197,12 @@
       <c r="B8" s="2" t="n">
         <v>45584.5625</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">vitality stadium
@@ -856,6 +1243,38 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>334</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>645000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>262000000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>337</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -867,7 +1286,12 @@
       <c r="B9" s="2" t="n">
         <v>45585.41666666666</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
@@ -909,6 +1333,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -919,7 +1359,12 @@
       <c r="B10" s="2" t="n">
         <v>45585.52083333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">anfield
@@ -961,6 +1406,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -971,7 +1432,12 @@
       <c r="B11" s="2" t="n">
         <v>45586.66666666666</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">city ground
@@ -1013,6 +1479,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1065,6 +1547,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1117,6 +1615,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1169,6 +1683,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1221,6 +1751,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1273,6 +1819,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1325,6 +1887,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1377,6 +1955,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1429,6 +2023,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -1481,6 +2091,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -1533,6 +2159,22 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -720,52 +720,52 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>190</v>
+        <v>186.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="R3" t="n">
-        <v>66000</v>
+        <v>129000</v>
       </c>
       <c r="S3" t="n">
-        <v>4200000</v>
+        <v>10200000</v>
       </c>
       <c r="T3" t="n">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="W3" t="n">
-        <v>178</v>
+        <v>180.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="n">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Z3" t="n">
-        <v>130000</v>
+        <v>240000</v>
       </c>
       <c r="AA3" t="n">
-        <v>29500000</v>
+        <v>57500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>184</v>
+        <v>182.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>141</v>
+        <v>280</v>
       </c>
       <c r="R4" t="n">
-        <v>48000</v>
+        <v>120000</v>
       </c>
       <c r="S4" t="n">
-        <v>4400000</v>
+        <v>8300000</v>
       </c>
       <c r="T4" t="n">
-        <v>143</v>
+        <v>289</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
         <v>21</v>
@@ -1035,34 +1035,34 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.8</v>
+        <v>26.25</v>
       </c>
       <c r="O6" t="n">
-        <v>187</v>
+        <v>185.75</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
-        <v>397</v>
+        <v>312</v>
       </c>
       <c r="R6" t="n">
-        <v>515000</v>
+        <v>360000</v>
       </c>
       <c r="S6" t="n">
-        <v>137100000</v>
+        <v>66100000</v>
       </c>
       <c r="T6" t="n">
-        <v>416</v>
+        <v>329</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="W6" t="n">
-        <v>185.5</v>
+        <v>186.5</v>
       </c>
       <c r="X6" t="n">
         <v>2</v>
@@ -1071,13 +1071,13 @@
         <v>162</v>
       </c>
       <c r="Z6" t="n">
-        <v>253000</v>
+        <v>266000</v>
       </c>
       <c r="AA6" t="n">
-        <v>69500000</v>
+        <v>66000000</v>
       </c>
       <c r="AB6" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AC6" t="n">
         <v>4</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="O7" t="n">
-        <v>186</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="R7" t="n">
-        <v>56000</v>
+        <v>99000</v>
       </c>
       <c r="S7" t="n">
-        <v>10800000</v>
+        <v>12800000</v>
       </c>
       <c r="T7" t="n">
-        <v>161</v>
+        <v>232</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>24.66666666666667</v>
@@ -1253,28 +1253,28 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>25.25</v>
+        <v>28.25</v>
       </c>
       <c r="W8" t="n">
-        <v>177.75</v>
+        <v>180.75</v>
       </c>
       <c r="X8" t="n">
         <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="Z8" t="n">
-        <v>645000</v>
+        <v>491000</v>
       </c>
       <c r="AA8" t="n">
-        <v>262000000</v>
+        <v>158900000</v>
       </c>
       <c r="AB8" t="n">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1333,22 +1333,54 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="O9" t="n">
+        <v>190.3333333333333</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>218</v>
+      </c>
+      <c r="R9" t="n">
+        <v>134000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>237</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>178.3333333333333</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>246</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>529000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,400 +493,1045 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.41666666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kavanagh c 
-  eng </t>
-        </is>
-      </c>
+        <v>45590.66666666666</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>481</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I3" t="n">
+        <v>481</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I4" t="n">
+        <v>481</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>31876</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>48</v>
+      </c>
+      <c r="I5" t="n">
+        <v>481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>481</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>48</v>
+      </c>
+      <c r="I7" t="n">
+        <v>481</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40341</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25486</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I9" t="n">
+        <v>481</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62500</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>48</v>
+      </c>
+      <c r="I10" t="n">
+        <v>481</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>481</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>52305</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29673</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61276</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>30404</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>32384</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">molineux stadium
   wolverhampton </t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E18" t="n">
         <v>31750</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>48</v>
-      </c>
-      <c r="I2" t="n">
-        <v>481</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>187</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>296</v>
-      </c>
-      <c r="R2" t="n">
-        <v>206000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>34300000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>315</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5</v>
-      </c>
-      <c r="V2" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="W2" t="n">
-        <v>178.3333333333333</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>246</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>529000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>118000000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>260</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>2ot8gOsJ</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brooks j 
-  eng </t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>61276</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>62850</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I19" t="n">
+        <v>481</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>75635</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>4fGZN2oK</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>48</v>
-      </c>
-      <c r="I3" t="n">
-        <v>481</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>27.66666666666667</v>
-      </c>
-      <c r="O3" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>247</v>
-      </c>
-      <c r="R3" t="n">
-        <v>286000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>101000000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>255</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W3" t="n">
-        <v>184.6666666666667</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>222</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>237000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>54500000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>247</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>KMCY9qSa</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>45586.66666666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>48</v>
-      </c>
-      <c r="I4" t="n">
-        <v>481</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>182.75</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>312</v>
-      </c>
-      <c r="R4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>57500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>317</v>
-      </c>
-      <c r="U4" t="n">
-        <v>8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>187</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>302</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>209000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>39400000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>481</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>26600</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" t="n">
+        <v>481</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -503,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45590.66666666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">king power stadium
@@ -544,6 +629,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>286</v>
+      </c>
+      <c r="R2" t="n">
+        <v>146000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>14200000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>298</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25</v>
+      </c>
+      <c r="W2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>156</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>117000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>35500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>161</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +688,12 @@
       <c r="B3" s="2" t="n">
         <v>45591.45833333334</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">villa park
@@ -596,6 +734,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N3" t="n">
+        <v>22</v>
+      </c>
+      <c r="O3" t="n">
+        <v>179</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>67000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>83</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>175</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>53000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +793,12 @@
       <c r="B4" s="2" t="n">
         <v>45591.45833333334</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">brentford community stadium
@@ -648,6 +839,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>177.75</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>309</v>
+      </c>
+      <c r="R4" t="n">
+        <v>258000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>316</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="X4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>354</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>161000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>367</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +898,12 @@
       <c r="B5" s="2" t="n">
         <v>45591.45833333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">amex stadium
@@ -700,6 +944,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N5" t="n">
+        <v>32</v>
+      </c>
+      <c r="O5" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>237</v>
+      </c>
+      <c r="R5" t="n">
+        <v>319000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>67800000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>237</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26</v>
+      </c>
+      <c r="W5" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>374</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>248000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>393</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +1003,12 @@
       <c r="B6" s="2" t="n">
         <v>45591.45833333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">etihad stadium
@@ -752,6 +1049,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N6" t="n">
+        <v>26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>402</v>
+      </c>
+      <c r="R6" t="n">
+        <v>713000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>421</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="W6" t="n">
+        <v>180</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>216</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>108000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>225</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -763,7 +1108,12 @@
       <c r="B7" s="2" t="n">
         <v>45591.5625</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">goodison park
@@ -804,6 +1154,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N7" t="n">
+        <v>22.14285714285714</v>
+      </c>
+      <c r="O7" t="n">
+        <v>186.5714285714286</v>
+      </c>
+      <c r="P7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>515</v>
+      </c>
+      <c r="R7" t="n">
+        <v>291000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>70900000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>565</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>306</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>288000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -815,7 +1213,12 @@
       <c r="B8" s="2" t="n">
         <v>45592.45833333334</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">stamford bridge
@@ -856,6 +1259,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>191</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>62</v>
+      </c>
+      <c r="R8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>80</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>312</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>360000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>66100000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>329</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -867,7 +1318,12 @@
       <c r="B9" s="2" t="n">
         <v>45592.45833333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">selhurst park
@@ -908,6 +1364,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N9" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="O9" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>228</v>
+      </c>
+      <c r="R9" t="n">
+        <v>178000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>36600000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>237</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>27</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>159</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>165</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -919,7 +1423,12 @@
       <c r="B10" s="2" t="n">
         <v>45592.45833333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">london stadium
@@ -960,6 +1469,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23</v>
+      </c>
+      <c r="O10" t="n">
+        <v>177</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>82</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>43500000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>395</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>439000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>412</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -971,7 +1528,12 @@
       <c r="B11" s="2" t="n">
         <v>45592.5625</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">emirates stadium
@@ -1013,525 +1575,53 @@
           <t>premier league</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>WIs9mjGL</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45598.39583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>52305</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>MqhPmaA4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>11307</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lb85TUOk</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>29673</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rc1ER8g2</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>61276</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>21YvrUwq</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>OGMmt88e</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45598.5</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>32384</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EJ4unbdE</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>drzevnw8</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.45833333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>62850</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>zil0kCo9</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
-        <v>481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ratYowuH</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>26600</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
+      <c r="N11" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>499</v>
+      </c>
+      <c r="R11" t="n">
+        <v>890000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>376500000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>511</v>
+      </c>
+      <c r="U11" t="n">
+        <v>18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="W11" t="n">
+        <v>180</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>327</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>393000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>156500000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>344</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="O2" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>388</v>
+      </c>
+      <c r="R2" t="n">
+        <v>450000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>73600000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>405</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W2" t="n">
+        <v>182</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>246</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>435000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>156500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +735,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>384</v>
+      </c>
+      <c r="R3" t="n">
+        <v>276000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>399</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="W3" t="n">
+        <v>179</v>
+      </c>
+      <c r="X3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>569</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1013000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>252000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>593</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +840,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>26.85714285714286</v>
+      </c>
+      <c r="O4" t="n">
+        <v>181.1428571428571</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>513</v>
+      </c>
+      <c r="R4" t="n">
+        <v>258000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>33500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>530</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="W4" t="n">
+        <v>184</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>285</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>129000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>17700000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>303</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +945,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="O5" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>252</v>
+      </c>
+      <c r="R5" t="n">
+        <v>346000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>144500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>260</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>185</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>316</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>408000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>79300000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>316</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +1050,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>181</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>212000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>240</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23</v>
+      </c>
+      <c r="W6" t="n">
+        <v>177</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>95000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>43500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -835,6 +1155,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>292</v>
+      </c>
+      <c r="R7" t="n">
+        <v>143000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>310</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>22</v>
+      </c>
+      <c r="W7" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>206000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>37100000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>403</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -892,6 +1260,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>453</v>
+      </c>
+      <c r="R8" t="n">
+        <v>319000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>56300000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>472</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.16666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>182.6666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>466</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>409000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>111100000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>485</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -949,6 +1365,38 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>394</v>
+      </c>
+      <c r="R9" t="n">
+        <v>449000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>415</v>
+      </c>
+      <c r="U9" t="n">
+        <v>12</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1006,6 +1454,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>389</v>
+      </c>
+      <c r="R10" t="n">
+        <v>389000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75500000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>406</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>21</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>144</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>135000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>166</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1063,526 +1559,22 @@
           <t>premier league</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>nX2mpxRQ</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>17250</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I12" t="n">
-        <v>481</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>YTzyyYmD</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>25486</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" t="n">
-        <v>481</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>K0RAmBXI</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">london stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>62500</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>48</v>
-      </c>
-      <c r="I14" t="n">
-        <v>481</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>0d4cBEPP</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45605.5</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>31750</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>WdKOwxDM</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>48</v>
-      </c>
-      <c r="I15" t="n">
-        <v>481</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HqKvGll</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45605.60416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>31876</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2XrRecc3</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="n">
-        <v>481</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0zTMbytK</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45605.70833333334</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>61276</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>W00wmLO0</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>48</v>
-      </c>
-      <c r="I17" t="n">
-        <v>481</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KK9ggF3s</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>75635</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>48</v>
-      </c>
-      <c r="I18" t="n">
-        <v>481</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hY71igYg</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30404</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I19" t="n">
-        <v>481</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>CzO2kX26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45606.45833333334</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>62850</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>48</v>
-      </c>
-      <c r="I20" t="n">
-        <v>481</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>CEnSxfJ0</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45606.5625</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>40341</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>48</v>
-      </c>
-      <c r="I21" t="n">
-        <v>481</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,119 +493,39 @@
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_home</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_home</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_home</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_home</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_away</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_miss_away</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>n_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>sum_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>sum_value_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.39583333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52305</v>
+        <v>17250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -629,88 +549,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N2" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>388</v>
-      </c>
-      <c r="R2" t="n">
-        <v>450000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>73600000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>405</v>
-      </c>
-      <c r="U2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V2" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="W2" t="n">
-        <v>182</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>246</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>435000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>156500000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">salisbury m 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11307</v>
+        <v>25486</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -734,88 +606,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>182.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>384</v>
-      </c>
-      <c r="R3" t="n">
-        <v>276000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>58000000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>399</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>25.71428571428572</v>
-      </c>
-      <c r="W3" t="n">
-        <v>179</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>569</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1013000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>252000000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>593</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29673</v>
+        <v>62500</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -839,88 +663,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N4" t="n">
-        <v>26.85714285714286</v>
-      </c>
-      <c r="O4" t="n">
-        <v>181.1428571428571</v>
-      </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>513</v>
-      </c>
-      <c r="R4" t="n">
-        <v>258000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>33500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>530</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="W4" t="n">
-        <v>184</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>285</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>129000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>17700000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>303</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">bramall t 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61276</v>
+        <v>31750</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -944,88 +720,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N5" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="O5" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>252</v>
-      </c>
-      <c r="R5" t="n">
-        <v>346000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>144500000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>260</v>
-      </c>
-      <c r="U5" t="n">
-        <v>9</v>
-      </c>
-      <c r="V5" t="n">
-        <v>32</v>
-      </c>
-      <c r="W5" t="n">
-        <v>185</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>316</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>408000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>79300000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>316</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30404</v>
+        <v>31876</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1049,88 +777,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N6" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="O6" t="n">
-        <v>181</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>235</v>
-      </c>
-      <c r="R6" t="n">
-        <v>212000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>52500000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>240</v>
-      </c>
-      <c r="U6" t="n">
-        <v>6</v>
-      </c>
-      <c r="V6" t="n">
-        <v>23</v>
-      </c>
-      <c r="W6" t="n">
-        <v>177</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>43500000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>86</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.5</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32384</v>
+        <v>61276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1154,88 +834,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N7" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>185.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>292</v>
-      </c>
-      <c r="R7" t="n">
-        <v>143000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>19300000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>310</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>186.2</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>365</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>206000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>37100000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>403</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31750</v>
+        <v>75635</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1259,88 +891,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N8" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="O8" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>453</v>
-      </c>
-      <c r="R8" t="n">
-        <v>319000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>56300000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>472</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.6666666666667</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>466</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>409000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>111100000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>485</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>62850</v>
+        <v>30404</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1365,71 +949,34 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O9" t="n">
-        <v>184.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>394</v>
-      </c>
-      <c r="R9" t="n">
-        <v>449000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>415</v>
-      </c>
-      <c r="U9" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
-        </is>
-      </c>
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75635</v>
+        <v>62850</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1453,88 +1000,40 @@
         <is>
           <t>premier league</t>
         </is>
-      </c>
-      <c r="N10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>389</v>
-      </c>
-      <c r="R10" t="n">
-        <v>389000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>75500000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>406</v>
-      </c>
-      <c r="U10" t="n">
-        <v>11</v>
-      </c>
-      <c r="V10" t="n">
-        <v>21</v>
-      </c>
-      <c r="W10" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>144</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>135000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>44500000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>166</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29589</v>
+        <v>40341</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1559,22 +1058,6 @@
           <t>premier league</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/england/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,86 @@
           <t>competition</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -550,6 +630,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N2" t="n">
+        <v>24</v>
+      </c>
+      <c r="O2" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>152</v>
+      </c>
+      <c r="R2" t="n">
+        <v>106000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>20500000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>162</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23</v>
+      </c>
+      <c r="W2" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>302</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>186000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>323</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -607,6 +735,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N3" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="O3" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>606</v>
+      </c>
+      <c r="R3" t="n">
+        <v>488000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>96200000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>629</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>183</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>63000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,6 +840,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N4" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>184</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>245</v>
+      </c>
+      <c r="R4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>97500000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>251</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>439</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>238000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>38400000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>477</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,6 +945,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N5" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>191</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>196000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>28150000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>396</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>179</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>363</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>180000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>16500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>378</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -778,6 +1050,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N6" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>382</v>
+      </c>
+      <c r="R6" t="n">
+        <v>442000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>81400000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>394</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>244</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>479000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>257</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -835,6 +1155,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>182</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>258</v>
+      </c>
+      <c r="R7" t="n">
+        <v>425000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>162500000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>259</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>157</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>195000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>32500000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>158</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -892,6 +1260,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>178.25</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>306</v>
+      </c>
+      <c r="R8" t="n">
+        <v>223000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>71500000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>338</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>185</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>97000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>222</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -949,6 +1365,54 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N9" t="n">
+        <v>26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>191</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>77</v>
+      </c>
+      <c r="R9" t="n">
+        <v>56000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>79</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24</v>
+      </c>
+      <c r="W9" t="n">
+        <v>190</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>229</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>225000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>47100000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>246</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -959,7 +1423,12 @@
       <c r="B10" s="2" t="n">
         <v>45606.45833333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">tottenham hotspur stadium
@@ -1000,6 +1469,54 @@
         <is>
           <t>premier league</t>
         </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>472</v>
+      </c>
+      <c r="R10" t="n">
+        <v>504000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>146500000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>496</v>
+      </c>
+      <c r="U10" t="n">
+        <v>14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>290</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>133000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>16900000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>298</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1058,6 +1575,530 @@
           <t>premier league</t>
         </is>
       </c>
+      <c r="N11" t="n">
+        <v>21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>144</v>
+      </c>
+      <c r="R11" t="n">
+        <v>135000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>44500000</v>
+      </c>
+      <c r="T11" t="n">
+        <v>166</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>403</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>597000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>413</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EubK3NNG</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>32261</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" t="n">
+        <v>481</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Cl3y4WHa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60704</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" t="n">
+        <v>481</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p21q2AnC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>42789</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WveT5hmm</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>11307</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>481</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>v3JHq2Wp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>39572</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>481</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69B375Oi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.5</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>29589</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>48</v>
+      </c>
+      <c r="I17" t="n">
+        <v>481</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>A7iT11hT</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>55097</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>48</v>
+      </c>
+      <c r="I18" t="n">
+        <v>481</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
